--- a/docs/MOJO_FPGA_pinout.xlsx
+++ b/docs/MOJO_FPGA_pinout.xlsx
@@ -9,12 +9,13 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="33060" windowHeight="17085" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33060" windowHeight="17085" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Nach FPGA Pin" sheetId="1" r:id="rId1"/>
     <sheet name="Nach SV Pin" sheetId="2" r:id="rId2"/>
-    <sheet name="Nach EPROM-Pin" sheetId="3" r:id="rId3"/>
+    <sheet name="Custom SV2" sheetId="4" r:id="rId3"/>
+    <sheet name="Nach EPROM-Pin" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="899" uniqueCount="328">
   <si>
     <t>P144</t>
   </si>
@@ -565,9 +566,6 @@
     <t xml:space="preserve">IO_L83N_VREF_3 </t>
   </si>
   <si>
-    <t>P31</t>
-  </si>
-  <si>
     <t>Function</t>
   </si>
   <si>
@@ -872,6 +870,147 @@
   </si>
   <si>
     <t># EPROM 2716..27512 UCF</t>
+  </si>
+  <si>
+    <t>PL3 40 Pin</t>
+  </si>
+  <si>
+    <t># PL3 Pin 1</t>
+  </si>
+  <si>
+    <t># PL3 Pin 2</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Custom</t>
+  </si>
+  <si>
+    <t>FPGA Name</t>
+  </si>
+  <si>
+    <t>FPGA Pin</t>
+  </si>
+  <si>
+    <t>SV2 Pin</t>
+  </si>
+  <si>
+    <t>UCF Data</t>
+  </si>
+  <si>
+    <t>HSYNC</t>
+  </si>
+  <si>
+    <t>VSYNC</t>
+  </si>
+  <si>
+    <t>BLUE(2)</t>
+  </si>
+  <si>
+    <t>BLUE(1)</t>
+  </si>
+  <si>
+    <t>BLUE(0)</t>
+  </si>
+  <si>
+    <t>VIDEO(0)</t>
+  </si>
+  <si>
+    <t>VIDEO(1)</t>
+  </si>
+  <si>
+    <t>VIDEO(2)</t>
+  </si>
+  <si>
+    <t>VIDEO(3)</t>
+  </si>
+  <si>
+    <t>VIDEO(4)</t>
+  </si>
+  <si>
+    <t>VIDEO(5)</t>
+  </si>
+  <si>
+    <t>VIDEO(6)</t>
+  </si>
+  <si>
+    <t>VIDEO(7)</t>
+  </si>
+  <si>
+    <t>COIN</t>
+  </si>
+  <si>
+    <t>START_1</t>
+  </si>
+  <si>
+    <t>LEFT</t>
+  </si>
+  <si>
+    <t>RIGHT</t>
+  </si>
+  <si>
+    <t>FIRE</t>
+  </si>
+  <si>
+    <t>START_2</t>
+  </si>
+  <si>
+    <t>UP</t>
+  </si>
+  <si>
+    <t>DOWN</t>
+  </si>
+  <si>
+    <t>LED(1)</t>
+  </si>
+  <si>
+    <t>LED(2)</t>
+  </si>
+  <si>
+    <t>LED(3)</t>
+  </si>
+  <si>
+    <t>LED(4)</t>
+  </si>
+  <si>
+    <t>LED(5)</t>
+  </si>
+  <si>
+    <t>LED(6)</t>
+  </si>
+  <si>
+    <t>LED(7)</t>
+  </si>
+  <si>
+    <t>CARRIER</t>
+  </si>
+  <si>
+    <t>GREEN(2)</t>
+  </si>
+  <si>
+    <t>GREEN(1)</t>
+  </si>
+  <si>
+    <t>GREEN(0)</t>
+  </si>
+  <si>
+    <t>RED(2)</t>
+  </si>
+  <si>
+    <t>RED(1)</t>
+  </si>
+  <si>
+    <t>RED(0)</t>
+  </si>
+  <si>
+    <t>AUDIO_PWM</t>
+  </si>
+  <si>
+    <t>LED(0)</t>
+  </si>
+  <si>
+    <t>P51</t>
   </si>
 </sst>
 </file>
@@ -954,7 +1093,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -991,6 +1130,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1004,7 +1149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1091,6 +1236,12 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1388,16 +1539,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="21" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>218</v>
-      </c>
       <c r="D1" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1405,7 +1556,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C2" s="2">
         <v>34</v>
@@ -1419,7 +1570,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C3" s="2">
         <v>33</v>
@@ -1433,7 +1584,7 @@
         <v>5</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C4" s="2">
         <v>32</v>
@@ -1447,7 +1598,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C5" s="2">
         <v>31</v>
@@ -1461,7 +1612,7 @@
         <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C6" s="2">
         <v>30</v>
@@ -1475,7 +1626,7 @@
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C7" s="2">
         <v>29</v>
@@ -1489,7 +1640,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C8" s="2">
         <v>28</v>
@@ -1503,7 +1654,7 @@
         <v>10</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C9" s="2">
         <v>27</v>
@@ -1517,7 +1668,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C10" s="2">
         <v>26</v>
@@ -1531,7 +1682,7 @@
         <v>12</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C11" s="2">
         <v>25</v>
@@ -1545,7 +1696,7 @@
         <v>14</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C12" s="2">
         <v>24</v>
@@ -1559,7 +1710,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C13" s="2">
         <v>23</v>
@@ -1573,7 +1724,7 @@
         <v>16</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C14" s="2">
         <v>22</v>
@@ -1587,7 +1738,7 @@
         <v>17</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C15" s="2">
         <v>21</v>
@@ -1601,7 +1752,7 @@
         <v>21</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C16" s="2">
         <v>20</v>
@@ -1615,7 +1766,7 @@
         <v>22</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C17" s="2">
         <v>19</v>
@@ -1629,7 +1780,7 @@
         <v>23</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C18" s="2">
         <v>18</v>
@@ -1643,7 +1794,7 @@
         <v>24</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C19" s="2">
         <v>17</v>
@@ -1657,7 +1808,7 @@
         <v>26</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C20" s="2">
         <v>16</v>
@@ -1671,7 +1822,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C21" s="2">
         <v>15</v>
@@ -1685,7 +1836,7 @@
         <v>29</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C22" s="2">
         <v>14</v>
@@ -1699,7 +1850,7 @@
         <v>30</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C23" s="2">
         <v>13</v>
@@ -1713,7 +1864,7 @@
         <v>32</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C24" s="2">
         <v>12</v>
@@ -1727,7 +1878,7 @@
         <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C25" s="2">
         <v>7</v>
@@ -1738,7 +1889,7 @@
         <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C26" s="2">
         <v>11</v>
@@ -1752,7 +1903,7 @@
         <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C27" s="2">
         <v>8</v>
@@ -1763,7 +1914,7 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C28" s="2">
         <v>10</v>
@@ -1777,7 +1928,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C29" s="2">
         <v>9</v>
@@ -1791,16 +1942,16 @@
         <v>37</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D30" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E30" s="25" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1808,19 +1959,19 @@
         <v>38</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C31" s="8">
         <v>49</v>
       </c>
       <c r="D31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E31" s="25" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1828,16 +1979,16 @@
         <v>39</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D32" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E32" s="25" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1845,7 +1996,7 @@
         <v>40</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C33" s="1">
         <v>8</v>
@@ -1860,7 +2011,7 @@
         <v>41</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C34" s="1">
         <v>7</v>
@@ -1875,16 +2026,16 @@
         <v>43</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D35" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E35" s="25" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1892,16 +2043,16 @@
         <v>44</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D36" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E36" s="25" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -1909,16 +2060,16 @@
         <v>45</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D37" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E37" s="25" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1926,16 +2077,16 @@
         <v>46</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D38" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E38" s="25" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -1943,13 +2094,13 @@
         <v>47</v>
       </c>
       <c r="D39" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -1957,16 +2108,16 @@
         <v>48</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D40" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E40" s="25" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -1974,13 +2125,13 @@
         <v>50</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C41" s="2">
         <v>6</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1988,13 +2139,13 @@
         <v>51</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C42" s="2">
         <v>5</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2029,13 +2180,13 @@
         <v>57</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C46" s="8">
         <v>8</v>
       </c>
       <c r="D46" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2052,13 +2203,13 @@
         <v>58</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C48" s="8">
         <v>7</v>
       </c>
       <c r="D48" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2075,13 +2226,13 @@
         <v>60</v>
       </c>
       <c r="D50" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E50" s="34" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2089,16 +2240,16 @@
         <v>61</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D51" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E51" s="25" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2106,16 +2257,16 @@
         <v>62</v>
       </c>
       <c r="B52" s="15" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D52" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E52" s="25" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2123,13 +2274,13 @@
         <v>64</v>
       </c>
       <c r="D53" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E53" s="33" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -2137,16 +2288,16 @@
         <v>65</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D54" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E54" s="25" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -2154,7 +2305,7 @@
         <v>66</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C55" s="8">
         <v>10</v>
@@ -2169,7 +2320,7 @@
         <v>67</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C56" s="8">
         <v>9</v>
@@ -2184,13 +2335,13 @@
         <v>69</v>
       </c>
       <c r="D57" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E57" s="33" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2198,16 +2349,16 @@
         <v>70</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D58" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E58" s="25" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2215,16 +2366,16 @@
         <v>71</v>
       </c>
       <c r="B59" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C59" s="8">
         <v>6</v>
       </c>
       <c r="D59" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2241,13 +2392,13 @@
         <v>73</v>
       </c>
       <c r="B61" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C61" s="8">
         <v>5</v>
       </c>
       <c r="D61" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F61" s="1"/>
     </row>
@@ -2256,16 +2407,16 @@
         <v>74</v>
       </c>
       <c r="B62" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C62" s="8">
         <v>12</v>
       </c>
       <c r="D62" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -2273,7 +2424,7 @@
         <v>75</v>
       </c>
       <c r="B63" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C63" s="8">
         <v>11</v>
@@ -2287,7 +2438,7 @@
         <v>78</v>
       </c>
       <c r="B64" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C64" s="8">
         <v>14</v>
@@ -2301,7 +2452,7 @@
         <v>79</v>
       </c>
       <c r="B65" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C65" s="8">
         <v>13</v>
@@ -2315,7 +2466,7 @@
         <v>80</v>
       </c>
       <c r="B66" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C66" s="8">
         <v>16</v>
@@ -2329,7 +2480,7 @@
         <v>81</v>
       </c>
       <c r="B67" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C67" s="8">
         <v>15</v>
@@ -2343,7 +2494,7 @@
         <v>82</v>
       </c>
       <c r="B68" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C68" s="8">
         <v>19</v>
@@ -2357,7 +2508,7 @@
         <v>83</v>
       </c>
       <c r="B69" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C69" s="8">
         <v>17</v>
@@ -2371,7 +2522,7 @@
         <v>84</v>
       </c>
       <c r="B70" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C70" s="8">
         <v>20</v>
@@ -2385,7 +2536,7 @@
         <v>85</v>
       </c>
       <c r="B71" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C71" s="8">
         <v>19</v>
@@ -2399,7 +2550,7 @@
         <v>87</v>
       </c>
       <c r="B72" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C72" s="8">
         <v>22</v>
@@ -2413,7 +2564,7 @@
         <v>88</v>
       </c>
       <c r="B73" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C73" s="8">
         <v>21</v>
@@ -2427,7 +2578,7 @@
         <v>92</v>
       </c>
       <c r="B74" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C74" s="8">
         <v>24</v>
@@ -2441,7 +2592,7 @@
         <v>93</v>
       </c>
       <c r="B75" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C75" s="8">
         <v>23</v>
@@ -2455,7 +2606,7 @@
         <v>94</v>
       </c>
       <c r="B76" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C76" s="8">
         <v>26</v>
@@ -2469,7 +2620,7 @@
         <v>95</v>
       </c>
       <c r="B77" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C77" s="8">
         <v>25</v>
@@ -2483,7 +2634,7 @@
         <v>97</v>
       </c>
       <c r="B78" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C78" s="8">
         <v>28</v>
@@ -2497,7 +2648,7 @@
         <v>98</v>
       </c>
       <c r="B79" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C79" s="8">
         <v>27</v>
@@ -2511,7 +2662,7 @@
         <v>99</v>
       </c>
       <c r="B80" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C80" s="8">
         <v>30</v>
@@ -2525,7 +2676,7 @@
         <v>100</v>
       </c>
       <c r="B81" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C81" s="8">
         <v>29</v>
@@ -2539,7 +2690,7 @@
         <v>101</v>
       </c>
       <c r="B82" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C82" s="8">
         <v>32</v>
@@ -2553,7 +2704,7 @@
         <v>102</v>
       </c>
       <c r="B83" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C83" s="8">
         <v>31</v>
@@ -2567,7 +2718,7 @@
         <v>104</v>
       </c>
       <c r="B84" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C84" s="8">
         <v>34</v>
@@ -2581,7 +2732,7 @@
         <v>105</v>
       </c>
       <c r="B85" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C85" s="8">
         <v>33</v>
@@ -2595,7 +2746,7 @@
         <v>106</v>
       </c>
       <c r="B86" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C86" s="8">
         <v>46</v>
@@ -2609,7 +2760,7 @@
         <v>107</v>
       </c>
       <c r="B87" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C87" s="8">
         <v>45</v>
@@ -2623,7 +2774,7 @@
         <v>109</v>
       </c>
       <c r="B88" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C88" s="8">
         <v>48</v>
@@ -2637,7 +2788,7 @@
         <v>110</v>
       </c>
       <c r="B89" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C89" s="8">
         <v>47</v>
@@ -2651,7 +2802,7 @@
         <v>111</v>
       </c>
       <c r="B90" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C90" s="8">
         <v>36</v>
@@ -2665,7 +2816,7 @@
         <v>112</v>
       </c>
       <c r="B91" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C91" s="8">
         <v>35</v>
@@ -2679,7 +2830,7 @@
         <v>114</v>
       </c>
       <c r="B92" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C92" s="8">
         <v>38</v>
@@ -2693,7 +2844,7 @@
         <v>115</v>
       </c>
       <c r="B93" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C93" s="8">
         <v>37</v>
@@ -2707,7 +2858,7 @@
         <v>116</v>
       </c>
       <c r="B94" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C94" s="8">
         <v>40</v>
@@ -2721,7 +2872,7 @@
         <v>117</v>
       </c>
       <c r="B95" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C95" s="8">
         <v>39</v>
@@ -2735,7 +2886,7 @@
         <v>118</v>
       </c>
       <c r="B96" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C96" s="8">
         <v>42</v>
@@ -2749,7 +2900,7 @@
         <v>119</v>
       </c>
       <c r="B97" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C97" s="8">
         <v>41</v>
@@ -2763,7 +2914,7 @@
         <v>120</v>
       </c>
       <c r="B98" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C98" s="8">
         <v>44</v>
@@ -2777,7 +2928,7 @@
         <v>121</v>
       </c>
       <c r="B99" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C99" s="8">
         <v>43</v>
@@ -2791,7 +2942,7 @@
         <v>123</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C100" s="2">
         <v>50</v>
@@ -2800,7 +2951,7 @@
         <v>31</v>
       </c>
       <c r="E100" s="32" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -2808,7 +2959,7 @@
         <v>124</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C101" s="2">
         <v>49</v>
@@ -2817,7 +2968,7 @@
         <v>29</v>
       </c>
       <c r="E101" s="32" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -2825,7 +2976,7 @@
         <v>126</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C102" s="2">
         <v>48</v>
@@ -2834,7 +2985,7 @@
         <v>27</v>
       </c>
       <c r="E102" s="32" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
@@ -2842,7 +2993,7 @@
         <v>127</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C103" s="2">
         <v>47</v>
@@ -2851,7 +3002,7 @@
         <v>25</v>
       </c>
       <c r="E103" s="32" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -2859,7 +3010,7 @@
         <v>131</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C104" s="2">
         <v>46</v>
@@ -2868,7 +3019,7 @@
         <v>23</v>
       </c>
       <c r="E104" s="32" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -2876,7 +3027,7 @@
         <v>132</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C105" s="2">
         <v>45</v>
@@ -2885,7 +3036,7 @@
         <v>21</v>
       </c>
       <c r="E105" s="32" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -2893,7 +3044,7 @@
         <v>133</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C106" s="2">
         <v>44</v>
@@ -2902,7 +3053,7 @@
         <v>19</v>
       </c>
       <c r="E106" s="32" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -2910,7 +3061,7 @@
         <v>134</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C107" s="2">
         <v>43</v>
@@ -2919,7 +3070,7 @@
         <v>17</v>
       </c>
       <c r="E107" s="32" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
@@ -2927,7 +3078,7 @@
         <v>137</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C108" s="2">
         <v>42</v>
@@ -2941,7 +3092,7 @@
         <v>138</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C109" s="2">
         <v>41</v>
@@ -2955,7 +3106,7 @@
         <v>139</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C110" s="2">
         <v>40</v>
@@ -2969,7 +3120,7 @@
         <v>140</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C111" s="2">
         <v>39</v>
@@ -2983,7 +3134,7 @@
         <v>141</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C112" s="2">
         <v>38</v>
@@ -2997,7 +3148,7 @@
         <v>142</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C113" s="2">
         <v>37</v>
@@ -3011,7 +3162,7 @@
         <v>143</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C114" s="2">
         <v>36</v>
@@ -3025,7 +3176,7 @@
         <v>144</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C115" s="2">
         <v>35</v>
@@ -3045,93 +3196,100 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:I113"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" customWidth="1"/>
     <col min="2" max="2" width="7.140625" style="4" customWidth="1"/>
     <col min="3" max="3" width="13.7109375" style="3" customWidth="1"/>
     <col min="4" max="4" width="30.7109375" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.85546875" customWidth="1"/>
-    <col min="7" max="7" width="13.5703125" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>218</v>
-      </c>
       <c r="C1" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>281</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B2" s="10">
         <v>1</v>
       </c>
       <c r="C2" s="12"/>
       <c r="D2" s="23" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E2" s="4"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F2" s="4"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B3" s="10">
         <v>2</v>
       </c>
       <c r="C3" s="12"/>
       <c r="D3" s="23" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="E3" s="4"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B4" s="10">
         <v>3</v>
       </c>
       <c r="C4" s="12"/>
       <c r="D4" s="23" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E4" s="4"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F4" s="4"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B5" s="10">
         <v>4</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="23" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="E5" s="4"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B6" s="10">
         <v>5</v>
@@ -3140,12 +3298,12 @@
         <v>107</v>
       </c>
       <c r="D6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B7" s="10">
         <v>6</v>
@@ -3154,15 +3312,15 @@
         <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>182</v>
-      </c>
-      <c r="F7" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+        <v>181</v>
+      </c>
+      <c r="G7" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B8" s="10">
         <v>7</v>
@@ -3171,16 +3329,16 @@
         <v>115</v>
       </c>
       <c r="D8" t="s">
-        <v>250</v>
-      </c>
-      <c r="F8" t="str">
+        <v>249</v>
+      </c>
+      <c r="G8" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,$A8,"_",B8,""" LOC = ",$C8," | IOSTANDARD = LVCMOS33;   # ",D8)</f>
         <v>NET "SV1_7" LOC = P58 | IOSTANDARD = LVCMOS33;   # IO_L14P_D11_2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B9" s="10">
         <v>8</v>
@@ -3189,16 +3347,16 @@
         <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>251</v>
-      </c>
-      <c r="F9" t="str">
-        <f t="shared" ref="F9:F45" si="0" xml:space="preserve"> CONCATENATE("NET """,$A9,"_",B9,""" LOC = ",$C9," | IOSTANDARD = LVCMOS33;   # ",D9)</f>
+        <v>250</v>
+      </c>
+      <c r="G9" t="str">
+        <f t="shared" ref="G9:G45" si="0" xml:space="preserve"> CONCATENATE("NET """,$A9,"_",B9,""" LOC = ",$C9," | IOSTANDARD = LVCMOS33;   # ",D9)</f>
         <v>NET "SV1_8" LOC = P57 | IOSTANDARD = LVCMOS33;   # IO_L14N_D12_2</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B10" s="10">
         <v>9</v>
@@ -3209,14 +3367,14 @@
       <c r="D10" t="s">
         <v>111</v>
       </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_9" LOC = P67 | IOSTANDARD = LVCMOS33;   # IO_L2P_CMPCLK_2 </v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B11" s="10">
         <v>10</v>
@@ -3227,14 +3385,14 @@
       <c r="D11" t="s">
         <v>113</v>
       </c>
-      <c r="F11" t="str">
+      <c r="G11" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_10" LOC = P66 | IOSTANDARD = LVCMOS33;   # IO_L2N_CMPMOSI_2 </v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B12" s="10">
         <v>11</v>
@@ -3245,14 +3403,14 @@
       <c r="D12" t="s">
         <v>105</v>
       </c>
-      <c r="F12" t="str">
+      <c r="G12" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_11" LOC = P75 | IOSTANDARD = LVCMOS33;   # IO_L74P_AWAKE_1 </v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B13" s="10">
         <v>12</v>
@@ -3261,16 +3419,16 @@
         <v>106</v>
       </c>
       <c r="D13" t="s">
-        <v>181</v>
-      </c>
-      <c r="F13" t="str">
+        <v>180</v>
+      </c>
+      <c r="G13" t="str">
         <f t="shared" si="0"/>
         <v>NET "SV1_12" LOC = P74 | IOSTANDARD = LVCMOS33;   # IO_L74N_DOUT_BUSY_1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B14" s="10">
         <v>13</v>
@@ -3281,14 +3439,14 @@
       <c r="D14" t="s">
         <v>101</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_13" LOC = P79 | IOSTANDARD = LVCMOS33;   # IO_L47P_1 </v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B15" s="10">
         <v>14</v>
@@ -3299,14 +3457,14 @@
       <c r="D15" t="s">
         <v>103</v>
       </c>
-      <c r="F15" t="str">
+      <c r="G15" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_14" LOC = P78 | IOSTANDARD = LVCMOS33;   # IO_L47N_1 </v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B16" s="10">
         <v>15</v>
@@ -3317,14 +3475,14 @@
       <c r="D16" t="s">
         <v>97</v>
       </c>
-      <c r="F16" t="str">
+      <c r="G16" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_15" LOC = P81 | IOSTANDARD = LVCMOS33;   # IO_L46P_1 </v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B17" s="10">
         <v>16</v>
@@ -3335,14 +3493,14 @@
       <c r="D17" t="s">
         <v>99</v>
       </c>
-      <c r="F17" t="str">
+      <c r="G17" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_16" LOC = P80 | IOSTANDARD = LVCMOS33;   # IO_L46N_1 </v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B18" s="10">
         <v>17</v>
@@ -3353,14 +3511,14 @@
       <c r="D18" t="s">
         <v>93</v>
       </c>
-      <c r="F18" t="str">
+      <c r="G18" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_17" LOC = P83 | IOSTANDARD = LVCMOS33;   # IO_L45P_1 </v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B19" s="10">
         <v>19</v>
@@ -3371,14 +3529,14 @@
       <c r="D19" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="F19" t="str">
+      <c r="G19" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_19" LOC = P85 | IOSTANDARD = LVCMOS33;   # IO_L43P_GCLK5_1 </v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B20" s="10">
         <v>19</v>
@@ -3389,14 +3547,14 @@
       <c r="D20" t="s">
         <v>95</v>
       </c>
-      <c r="F20" t="str">
+      <c r="G20" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_19" LOC = P82 | IOSTANDARD = LVCMOS33;   # IO_L45N_1 </v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B21" s="10">
         <v>20</v>
@@ -3407,14 +3565,14 @@
       <c r="D21" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="F21" t="str">
+      <c r="G21" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_20" LOC = P84 | IOSTANDARD = LVCMOS33;   # IO_L43N_GCLK4_1 </v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B22" s="10">
         <v>21</v>
@@ -3425,14 +3583,14 @@
       <c r="D22" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="F22" t="str">
+      <c r="G22" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_21" LOC = P88 | IOSTANDARD = LVCMOS33;   # IO_L42P_GCLK7_1 </v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B23" s="10">
         <v>22</v>
@@ -3444,16 +3602,16 @@
         <v>87</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="F23" t="str">
+        <v>237</v>
+      </c>
+      <c r="G23" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_22" LOC = P87 | IOSTANDARD = LVCMOS33;   # IO_L42N_GCLK6_TRDY1_1 </v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B24" s="10">
         <v>23</v>
@@ -3465,16 +3623,16 @@
         <v>81</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>239</v>
-      </c>
-      <c r="F24" t="str">
+        <v>238</v>
+      </c>
+      <c r="G24" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_23" LOC = P93 | IOSTANDARD = LVCMOS33;   # IO_L41P_GCLK9_IRDY1_1 </v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B25" s="10">
         <v>24</v>
@@ -3486,16 +3644,16 @@
         <v>83</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="F25" t="str">
+        <v>239</v>
+      </c>
+      <c r="G25" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_24" LOC = P92 | IOSTANDARD = LVCMOS33;   # IO_L41N_GCLK8_1 </v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B26" s="10">
         <v>25</v>
@@ -3507,16 +3665,16 @@
         <v>77</v>
       </c>
       <c r="E26" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="F26" t="str">
+        <v>240</v>
+      </c>
+      <c r="G26" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_25" LOC = P95 | IOSTANDARD = LVCMOS33;   # IO_L40P_GCLK11_1 </v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B27" s="10">
         <v>26</v>
@@ -3528,16 +3686,16 @@
         <v>79</v>
       </c>
       <c r="E27" s="25" t="s">
-        <v>242</v>
-      </c>
-      <c r="F27" t="str">
+        <v>241</v>
+      </c>
+      <c r="G27" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_26" LOC = P94 | IOSTANDARD = LVCMOS33;   # IO_L40N_GCLK10_1 </v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B28" s="10">
         <v>27</v>
@@ -3548,14 +3706,14 @@
       <c r="D28" t="s">
         <v>73</v>
       </c>
-      <c r="F28" t="str">
+      <c r="G28" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_27" LOC = P98 | IOSTANDARD = LVCMOS33;   # IO_L34P_1 </v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B29" s="10">
         <v>28</v>
@@ -3566,14 +3724,14 @@
       <c r="D29" t="s">
         <v>75</v>
       </c>
-      <c r="F29" t="str">
+      <c r="G29" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_28" LOC = P97 | IOSTANDARD = LVCMOS33;   # IO_L34N_1 </v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B30" s="10">
         <v>29</v>
@@ -3584,14 +3742,14 @@
       <c r="D30" t="s">
         <v>69</v>
       </c>
-      <c r="F30" t="str">
+      <c r="G30" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_29" LOC = P100 | IOSTANDARD = LVCMOS33;   # IO_L33P_1 </v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B31" s="10">
         <v>30</v>
@@ -3602,14 +3760,14 @@
       <c r="D31" t="s">
         <v>71</v>
       </c>
-      <c r="F31" t="str">
+      <c r="G31" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_30" LOC = P99 | IOSTANDARD = LVCMOS33;   # IO_L33N_1 </v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B32" s="10">
         <v>31</v>
@@ -3620,14 +3778,14 @@
       <c r="D32" t="s">
         <v>65</v>
       </c>
-      <c r="F32" t="str">
+      <c r="G32" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_31" LOC = P102 | IOSTANDARD = LVCMOS33;   # IO_L32P_1 </v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B33" s="10">
         <v>32</v>
@@ -3638,14 +3796,14 @@
       <c r="D33" t="s">
         <v>67</v>
       </c>
-      <c r="F33" t="str">
+      <c r="G33" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_32" LOC = P101 | IOSTANDARD = LVCMOS33;   # IO_L32N_1 </v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B34" s="10">
         <v>33</v>
@@ -3656,14 +3814,14 @@
       <c r="D34" t="s">
         <v>61</v>
       </c>
-      <c r="F34" t="str">
+      <c r="G34" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_33" LOC = P105 | IOSTANDARD = LVCMOS33;   # IO_L1P_1 </v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B35" s="10">
         <v>34</v>
@@ -3674,14 +3832,14 @@
       <c r="D35" t="s">
         <v>63</v>
       </c>
-      <c r="F35" t="str">
+      <c r="G35" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_34" LOC = P104 | IOSTANDARD = LVCMOS33;   # IO_L1N_VREF_1 </v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B36" s="10">
         <v>35</v>
@@ -3692,14 +3850,14 @@
       <c r="D36" t="s">
         <v>49</v>
       </c>
-      <c r="F36" t="str">
+      <c r="G36" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_35" LOC = P112 | IOSTANDARD = LVCMOS33;   # IO_L66P_SCP1_0 </v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B37" s="10">
         <v>36</v>
@@ -3710,14 +3868,14 @@
       <c r="D37" t="s">
         <v>51</v>
       </c>
-      <c r="F37" t="str">
+      <c r="G37" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_36" LOC = P111 | IOSTANDARD = LVCMOS33;   # IO_L66N_SCP0_0 </v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B38" s="10">
         <v>37</v>
@@ -3728,14 +3886,14 @@
       <c r="D38" t="s">
         <v>45</v>
       </c>
-      <c r="F38" t="str">
+      <c r="G38" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_37" LOC = P115 | IOSTANDARD = LVCMOS33;   # IO_L65P_SCP3_0 </v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B39" s="10">
         <v>38</v>
@@ -3746,14 +3904,14 @@
       <c r="D39" t="s">
         <v>47</v>
       </c>
-      <c r="F39" t="str">
+      <c r="G39" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_38" LOC = P114 | IOSTANDARD = LVCMOS33;   # IO_L65N_SCP2_0 </v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B40" s="10">
         <v>39</v>
@@ -3764,14 +3922,14 @@
       <c r="D40" t="s">
         <v>41</v>
       </c>
-      <c r="F40" t="str">
+      <c r="G40" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_39" LOC = P117 | IOSTANDARD = LVCMOS33;   # IO_L64P_SCP5_0 </v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B41" s="10">
         <v>40</v>
@@ -3782,14 +3940,14 @@
       <c r="D41" t="s">
         <v>43</v>
       </c>
-      <c r="F41" t="str">
+      <c r="G41" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_40" LOC = P116 | IOSTANDARD = LVCMOS33;   # IO_L64N_SCP4_0 </v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B42" s="10">
         <v>41</v>
@@ -3800,14 +3958,14 @@
       <c r="D42" t="s">
         <v>37</v>
       </c>
-      <c r="F42" t="str">
+      <c r="G42" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_41" LOC = P119 | IOSTANDARD = LVCMOS33;   # IO_L63P_SCP7_0 </v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B43" s="10">
         <v>42</v>
@@ -3818,14 +3976,14 @@
       <c r="D43" t="s">
         <v>39</v>
       </c>
-      <c r="F43" t="str">
+      <c r="G43" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_42" LOC = P118 | IOSTANDARD = LVCMOS33;   # IO_L63N_SCP6_0 </v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B44" s="10">
         <v>43</v>
@@ -3836,14 +3994,14 @@
       <c r="D44" t="s">
         <v>33</v>
       </c>
-      <c r="F44" t="str">
+      <c r="G44" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_43" LOC = P121 | IOSTANDARD = LVCMOS33;   # IO_L62P_0 </v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B45" s="10">
         <v>44</v>
@@ -3854,14 +4012,14 @@
       <c r="D45" t="s">
         <v>35</v>
       </c>
-      <c r="F45" t="str">
+      <c r="G45" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">NET "SV1_44" LOC = P120 | IOSTANDARD = LVCMOS33;   # IO_L62N_VREF_0 </v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B46" s="10">
         <v>45</v>
@@ -3873,12 +4031,12 @@
         <v>57</v>
       </c>
       <c r="E46" s="25" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B47" s="10">
         <v>46</v>
@@ -3890,12 +4048,12 @@
         <v>59</v>
       </c>
       <c r="E47" s="25" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B48" s="10">
         <v>47</v>
@@ -3907,12 +4065,12 @@
         <v>55</v>
       </c>
       <c r="E48" s="25" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B49" s="10">
         <v>48</v>
@@ -3924,12 +4082,12 @@
         <v>53</v>
       </c>
       <c r="E49" s="25" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B50" s="10">
         <v>49</v>
@@ -3938,106 +4096,119 @@
         <v>126</v>
       </c>
       <c r="D50" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E50" s="25" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B51" s="10">
         <v>50</v>
       </c>
       <c r="C51" s="12"/>
       <c r="D51" s="23" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52"/>
       <c r="B52"/>
       <c r="C52"/>
-      <c r="G52" s="3"/>
+      <c r="F52" s="18" t="s">
+        <v>281</v>
+      </c>
       <c r="H52" s="3"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I52" s="3"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B53" s="11">
         <v>1</v>
       </c>
       <c r="C53" s="13"/>
       <c r="D53" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="F53" s="9"/>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+      <c r="F53" s="36">
+        <v>1</v>
+      </c>
+      <c r="G53" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B54" s="11">
         <v>2</v>
       </c>
       <c r="C54" s="13"/>
       <c r="D54" s="23" t="s">
-        <v>256</v>
-      </c>
-      <c r="F54" s="9"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="F54" s="36">
+        <v>2</v>
+      </c>
+      <c r="G54" s="9" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B55" s="11">
         <v>3</v>
       </c>
       <c r="C55" s="13"/>
       <c r="D55" s="23" t="s">
-        <v>255</v>
-      </c>
-      <c r="F55" s="9"/>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+      <c r="G55" s="9"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B56" s="11">
         <v>4</v>
       </c>
       <c r="C56" s="13"/>
       <c r="D56" s="23" t="s">
-        <v>257</v>
-      </c>
-      <c r="F56" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+        <v>256</v>
+      </c>
+      <c r="G56" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B57" s="11">
         <v>5</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>179</v>
+        <v>327</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="F57" t="str">
-        <f t="shared" ref="F57:F102" si="1" xml:space="preserve"> CONCATENATE("NET """,$A57,"_",B57,""" LOC = ",$C57," | IOSTANDARD = LVCMOS33;   # ",D57)</f>
-        <v>NET "SV2_5" LOC = P31 | IOSTANDARD = LVCMOS33;   # IO_L31P_GCLK31_D14_2</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+        <v>248</v>
+      </c>
+      <c r="G57" t="str">
+        <f t="shared" ref="G57:G102" si="1" xml:space="preserve"> CONCATENATE("NET """,$A57,"_",B57,""" LOC = ",$C57," | IOSTANDARD = LVCMOS33;   # ",D57)</f>
+        <v>NET "SV2_5" LOC = P51 | IOSTANDARD = LVCMOS33;   # IO_L31P_GCLK31_D14_2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B58" s="11">
         <v>6</v>
@@ -4046,16 +4217,16 @@
         <v>121</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="F58" t="str">
+        <v>247</v>
+      </c>
+      <c r="G58" t="str">
         <f t="shared" si="1"/>
         <v>NET "SV2_6" LOC = P50 | IOSTANDARD = LVCMOS33;   # IO_L31N_GCLK30_D15_2</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B59" s="11">
         <v>7</v>
@@ -4064,16 +4235,16 @@
         <v>122</v>
       </c>
       <c r="D59" t="s">
-        <v>246</v>
-      </c>
-      <c r="F59" t="str">
+        <v>245</v>
+      </c>
+      <c r="G59" t="str">
         <f t="shared" si="1"/>
         <v>NET "SV2_7" LOC = P41 | IOSTANDARD = LVCMOS33;   # IO_L64P_2</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B60" s="11">
         <v>8</v>
@@ -4082,16 +4253,16 @@
         <v>124</v>
       </c>
       <c r="D60" t="s">
-        <v>247</v>
-      </c>
-      <c r="F60" t="str">
+        <v>246</v>
+      </c>
+      <c r="G60" t="str">
         <f t="shared" si="1"/>
         <v>NET "SV2_8" LOC = P40 | IOSTANDARD = LVCMOS33;   # IO_L64N_2</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B61" s="11">
         <v>9</v>
@@ -4102,14 +4273,14 @@
       <c r="D61" t="s">
         <v>128</v>
       </c>
-      <c r="F61" t="str">
+      <c r="G61" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">NET "SV2_9" LOC = P35 | IOSTANDARD = LVCMOS33;   # IO_L1P_3 </v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B62" s="11">
         <v>10</v>
@@ -4120,14 +4291,14 @@
       <c r="D62" t="s">
         <v>130</v>
       </c>
-      <c r="F62" t="str">
+      <c r="G62" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">NET "SV2_10" LOC = P34 | IOSTANDARD = LVCMOS33;   # IO_L1N_VREF_3 </v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B63" s="11">
         <v>11</v>
@@ -4138,14 +4309,17 @@
       <c r="D63" t="s">
         <v>132</v>
       </c>
-      <c r="F63" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_11" LOC = P33 | IOSTANDARD = LVCMOS33;   # IO_L2P_3 </v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F63" s="37">
+        <v>3</v>
+      </c>
+      <c r="G63" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,$A63,"_",B63,""" LOC = ",$C63," | IOSTANDARD = LVCMOS33;   # ",D63," ### PL3 Pin ",F63)</f>
+        <v>NET "SV2_11" LOC = P33 | IOSTANDARD = LVCMOS33;   # IO_L2P_3  ### PL3 Pin 3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B64" s="11">
         <v>12</v>
@@ -4156,14 +4330,17 @@
       <c r="D64" t="s">
         <v>134</v>
       </c>
-      <c r="F64" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_12" LOC = P32 | IOSTANDARD = LVCMOS33;   # IO_L2N_3 </v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F64" s="37">
+        <v>4</v>
+      </c>
+      <c r="G64" t="str">
+        <f t="shared" ref="G64:G100" si="2" xml:space="preserve"> CONCATENATE("NET """,$A64,"_",B64,""" LOC = ",$C64," | IOSTANDARD = LVCMOS33;   # ",D64," ### PL3 Pin ",F64)</f>
+        <v>NET "SV2_12" LOC = P32 | IOSTANDARD = LVCMOS33;   # IO_L2N_3  ### PL3 Pin 4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B65" s="11">
         <v>13</v>
@@ -4174,14 +4351,17 @@
       <c r="D65" t="s">
         <v>136</v>
       </c>
-      <c r="F65" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_13" LOC = P30 | IOSTANDARD = LVCMOS33;   # IO_L36P_3 </v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F65" s="37">
+        <v>5</v>
+      </c>
+      <c r="G65" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_13" LOC = P30 | IOSTANDARD = LVCMOS33;   # IO_L36P_3  ### PL3 Pin 5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B66" s="11">
         <v>14</v>
@@ -4192,14 +4372,17 @@
       <c r="D66" t="s">
         <v>138</v>
       </c>
-      <c r="F66" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_14" LOC = P29 | IOSTANDARD = LVCMOS33;   # IO_L36N_3 </v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F66" s="37">
+        <v>6</v>
+      </c>
+      <c r="G66" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_14" LOC = P29 | IOSTANDARD = LVCMOS33;   # IO_L36N_3  ### PL3 Pin 6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B67" s="11">
         <v>15</v>
@@ -4210,14 +4393,17 @@
       <c r="D67" t="s">
         <v>140</v>
       </c>
-      <c r="F67" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_15" LOC = P27 | IOSTANDARD = LVCMOS33;   # IO_L37P_3 </v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F67" s="37">
+        <v>7</v>
+      </c>
+      <c r="G67" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_15" LOC = P27 | IOSTANDARD = LVCMOS33;   # IO_L37P_3  ### PL3 Pin 7</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B68" s="11">
         <v>16</v>
@@ -4228,14 +4414,17 @@
       <c r="D68" t="s">
         <v>142</v>
       </c>
-      <c r="F68" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_16" LOC = P26 | IOSTANDARD = LVCMOS33;   # IO_L37N_3 </v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F68" s="37">
+        <v>8</v>
+      </c>
+      <c r="G68" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_16" LOC = P26 | IOSTANDARD = LVCMOS33;   # IO_L37N_3  ### PL3 Pin 8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B69" s="11">
         <v>17</v>
@@ -4246,14 +4435,17 @@
       <c r="D69" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F69" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_17" LOC = P24 | IOSTANDARD = LVCMOS33;   # IO_L41P_GCLK27_3 </v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F69" s="37">
+        <v>9</v>
+      </c>
+      <c r="G69" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_17" LOC = P24 | IOSTANDARD = LVCMOS33;   # IO_L41P_GCLK27_3  ### PL3 Pin 9</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B70" s="11">
         <v>18</v>
@@ -4264,14 +4456,17 @@
       <c r="D70" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="F70" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_18" LOC = P23 | IOSTANDARD = LVCMOS33;   # IO_L41N_GCLK26_3 </v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F70" s="37">
+        <v>10</v>
+      </c>
+      <c r="G70" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_18" LOC = P23 | IOSTANDARD = LVCMOS33;   # IO_L41N_GCLK26_3  ### PL3 Pin 10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B71" s="11">
         <v>19</v>
@@ -4282,14 +4477,17 @@
       <c r="D71" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F71" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_19" LOC = P22 | IOSTANDARD = LVCMOS33;   # IO_L42P_GCLK25_TRDY2_3 </v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F71" s="37">
+        <v>11</v>
+      </c>
+      <c r="G71" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_19" LOC = P22 | IOSTANDARD = LVCMOS33;   # IO_L42P_GCLK25_TRDY2_3  ### PL3 Pin 11</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B72" s="11">
         <v>20</v>
@@ -4300,14 +4498,17 @@
       <c r="D72" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="F72" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_20" LOC = P21 | IOSTANDARD = LVCMOS33;   # IO_L42N_GCLK24_3 </v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F72" s="37">
+        <v>12</v>
+      </c>
+      <c r="G72" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_20" LOC = P21 | IOSTANDARD = LVCMOS33;   # IO_L42N_GCLK24_3  ### PL3 Pin 12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B73" s="11">
         <v>21</v>
@@ -4318,14 +4519,17 @@
       <c r="D73" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="F73" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_21" LOC = P17 | IOSTANDARD = LVCMOS33;   # IO_L43P_GCLK23_3 </v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F73" s="37">
+        <v>13</v>
+      </c>
+      <c r="G73" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_21" LOC = P17 | IOSTANDARD = LVCMOS33;   # IO_L43P_GCLK23_3  ### PL3 Pin 13</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B74" s="11">
         <v>22</v>
@@ -4336,14 +4540,17 @@
       <c r="D74" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="F74" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_22" LOC = P16 | IOSTANDARD = LVCMOS33;   # IO_L43N_GCLK22_IRDY2_3 </v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F74" s="37">
+        <v>14</v>
+      </c>
+      <c r="G74" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_22" LOC = P16 | IOSTANDARD = LVCMOS33;   # IO_L43N_GCLK22_IRDY2_3  ### PL3 Pin 14</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B75" s="11">
         <v>23</v>
@@ -4354,14 +4561,17 @@
       <c r="D75" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="F75" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_23" LOC = P15 | IOSTANDARD = LVCMOS33;   # IO_L44P_GCLK21_3 </v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F75" s="37">
+        <v>15</v>
+      </c>
+      <c r="G75" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_23" LOC = P15 | IOSTANDARD = LVCMOS33;   # IO_L44P_GCLK21_3  ### PL3 Pin 15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B76" s="11">
         <v>24</v>
@@ -4372,16 +4582,19 @@
       <c r="D76" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="F76" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_24" LOC = P14 | IOSTANDARD = LVCMOS33;   # IO_L44N_GCLK20_3 </v>
-      </c>
-      <c r="G76" s="5"/>
+      <c r="F76" s="37">
+        <v>16</v>
+      </c>
+      <c r="G76" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_24" LOC = P14 | IOSTANDARD = LVCMOS33;   # IO_L44N_GCLK20_3  ### PL3 Pin 16</v>
+      </c>
       <c r="H76" s="5"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I76" s="5"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B77" s="11">
         <v>25</v>
@@ -4392,14 +4605,17 @@
       <c r="D77" t="s">
         <v>160</v>
       </c>
-      <c r="F77" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_25" LOC = P12 | IOSTANDARD = LVCMOS33;   # IO_L49P_3 </v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F77" s="37">
+        <v>17</v>
+      </c>
+      <c r="G77" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_25" LOC = P12 | IOSTANDARD = LVCMOS33;   # IO_L49P_3  ### PL3 Pin 17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B78" s="11">
         <v>26</v>
@@ -4410,14 +4626,17 @@
       <c r="D78" t="s">
         <v>162</v>
       </c>
-      <c r="F78" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_26" LOC = P11 | IOSTANDARD = LVCMOS33;   # IO_L49N_3 </v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F78" s="37">
+        <v>18</v>
+      </c>
+      <c r="G78" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_26" LOC = P11 | IOSTANDARD = LVCMOS33;   # IO_L49N_3  ### PL3 Pin 18</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B79" s="11">
         <v>27</v>
@@ -4428,14 +4647,17 @@
       <c r="D79" t="s">
         <v>164</v>
       </c>
-      <c r="F79" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_27" LOC = P10 | IOSTANDARD = LVCMOS33;   # IO_L50P_3 </v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F79" s="37">
+        <v>19</v>
+      </c>
+      <c r="G79" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_27" LOC = P10 | IOSTANDARD = LVCMOS33;   # IO_L50P_3  ### PL3 Pin 19</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B80" s="11">
         <v>28</v>
@@ -4446,16 +4668,19 @@
       <c r="D80" t="s">
         <v>166</v>
       </c>
-      <c r="F80" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_28" LOC = P9 | IOSTANDARD = LVCMOS33;   # IO_L50N_3 </v>
-      </c>
-      <c r="G80" s="5"/>
+      <c r="F80" s="37">
+        <v>20</v>
+      </c>
+      <c r="G80" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_28" LOC = P9 | IOSTANDARD = LVCMOS33;   # IO_L50N_3  ### PL3 Pin 20</v>
+      </c>
       <c r="H80" s="5"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="I80" s="5"/>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B81" s="11">
         <v>29</v>
@@ -4466,14 +4691,17 @@
       <c r="D81" t="s">
         <v>168</v>
       </c>
-      <c r="F81" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_29" LOC = P8 | IOSTANDARD = LVCMOS33;   # IO_L51P_3 </v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F81" s="37">
+        <v>21</v>
+      </c>
+      <c r="G81" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_29" LOC = P8 | IOSTANDARD = LVCMOS33;   # IO_L51P_3  ### PL3 Pin 21</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B82" s="11">
         <v>30</v>
@@ -4484,14 +4712,17 @@
       <c r="D82" t="s">
         <v>170</v>
       </c>
-      <c r="F82" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_30" LOC = P7 | IOSTANDARD = LVCMOS33;   # IO_L51N_3 </v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F82" s="37">
+        <v>22</v>
+      </c>
+      <c r="G82" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_30" LOC = P7 | IOSTANDARD = LVCMOS33;   # IO_L51N_3  ### PL3 Pin 22</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B83" s="11">
         <v>31</v>
@@ -4502,14 +4733,17 @@
       <c r="D83" t="s">
         <v>172</v>
       </c>
-      <c r="F83" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_31" LOC = P6 | IOSTANDARD = LVCMOS33;   # IO_L52P_3 </v>
-      </c>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F83" s="37">
+        <v>23</v>
+      </c>
+      <c r="G83" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_31" LOC = P6 | IOSTANDARD = LVCMOS33;   # IO_L52P_3  ### PL3 Pin 23</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B84" s="11">
         <v>32</v>
@@ -4520,14 +4754,17 @@
       <c r="D84" t="s">
         <v>174</v>
       </c>
-      <c r="F84" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_32" LOC = P5 | IOSTANDARD = LVCMOS33;   # IO_L52N_3 </v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F84" s="37">
+        <v>24</v>
+      </c>
+      <c r="G84" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_32" LOC = P5 | IOSTANDARD = LVCMOS33;   # IO_L52N_3  ### PL3 Pin 24</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B85" s="11">
         <v>33</v>
@@ -4538,14 +4775,17 @@
       <c r="D85" t="s">
         <v>176</v>
       </c>
-      <c r="F85" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_33" LOC = P2 | IOSTANDARD = LVCMOS33;   # IO_L83P_3 </v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F85" s="37">
+        <v>25</v>
+      </c>
+      <c r="G85" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_33" LOC = P2 | IOSTANDARD = LVCMOS33;   # IO_L83P_3  ### PL3 Pin 25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B86" s="11">
         <v>34</v>
@@ -4556,14 +4796,17 @@
       <c r="D86" t="s">
         <v>178</v>
       </c>
-      <c r="F86" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_34" LOC = P1 | IOSTANDARD = LVCMOS33;   # IO_L83N_VREF_3 </v>
-      </c>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F86" s="37">
+        <v>26</v>
+      </c>
+      <c r="G86" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_34" LOC = P1 | IOSTANDARD = LVCMOS33;   # IO_L83N_VREF_3  ### PL3 Pin 26</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B87" s="11">
         <v>35</v>
@@ -4574,14 +4817,17 @@
       <c r="D87" t="s">
         <v>1</v>
       </c>
-      <c r="F87" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_35" LOC = P144 | IOSTANDARD = LVCMOS33;   # IO_L1P_HSWAPEN_0 </v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F87" s="37">
+        <v>27</v>
+      </c>
+      <c r="G87" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_35" LOC = P144 | IOSTANDARD = LVCMOS33;   # IO_L1P_HSWAPEN_0  ### PL3 Pin 27</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B88" s="11">
         <v>36</v>
@@ -4592,14 +4838,17 @@
       <c r="D88" t="s">
         <v>3</v>
       </c>
-      <c r="F88" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_36" LOC = P143 | IOSTANDARD = LVCMOS33;   # IO_L1N_VREF_0 </v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F88" s="37">
+        <v>28</v>
+      </c>
+      <c r="G88" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_36" LOC = P143 | IOSTANDARD = LVCMOS33;   # IO_L1N_VREF_0  ### PL3 Pin 28</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B89" s="11">
         <v>37</v>
@@ -4610,14 +4859,17 @@
       <c r="D89" t="s">
         <v>5</v>
       </c>
-      <c r="F89" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_37" LOC = P142 | IOSTANDARD = LVCMOS33;   # IO_L2P_0 </v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F89" s="37">
+        <v>29</v>
+      </c>
+      <c r="G89" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_37" LOC = P142 | IOSTANDARD = LVCMOS33;   # IO_L2P_0  ### PL3 Pin 29</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B90" s="11">
         <v>38</v>
@@ -4628,14 +4880,17 @@
       <c r="D90" t="s">
         <v>7</v>
       </c>
-      <c r="F90" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_38" LOC = P141 | IOSTANDARD = LVCMOS33;   # IO_L2N_0 </v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F90" s="37">
+        <v>30</v>
+      </c>
+      <c r="G90" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_38" LOC = P141 | IOSTANDARD = LVCMOS33;   # IO_L2N_0  ### PL3 Pin 30</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B91" s="11">
         <v>39</v>
@@ -4646,14 +4901,17 @@
       <c r="D91" t="s">
         <v>9</v>
       </c>
-      <c r="F91" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_39" LOC = P140 | IOSTANDARD = LVCMOS33;   # IO_L3P_0 </v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F91" s="37">
+        <v>31</v>
+      </c>
+      <c r="G91" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_39" LOC = P140 | IOSTANDARD = LVCMOS33;   # IO_L3P_0  ### PL3 Pin 31</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B92" s="11">
         <v>40</v>
@@ -4664,14 +4922,17 @@
       <c r="D92" t="s">
         <v>11</v>
       </c>
-      <c r="F92" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_40" LOC = P139 | IOSTANDARD = LVCMOS33;   # IO_L3N_0 </v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F92" s="37">
+        <v>32</v>
+      </c>
+      <c r="G92" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_40" LOC = P139 | IOSTANDARD = LVCMOS33;   # IO_L3N_0  ### PL3 Pin 32</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B93" s="11">
         <v>41</v>
@@ -4682,14 +4943,17 @@
       <c r="D93" t="s">
         <v>13</v>
       </c>
-      <c r="F93" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_41" LOC = P138 | IOSTANDARD = LVCMOS33;   # IO_L4P_0 </v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F93" s="37">
+        <v>33</v>
+      </c>
+      <c r="G93" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_41" LOC = P138 | IOSTANDARD = LVCMOS33;   # IO_L4P_0  ### PL3 Pin 33</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B94" s="11">
         <v>42</v>
@@ -4700,14 +4964,17 @@
       <c r="D94" t="s">
         <v>15</v>
       </c>
-      <c r="F94" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_42" LOC = P137 | IOSTANDARD = LVCMOS33;   # IO_L4N_0 </v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F94" s="37">
+        <v>34</v>
+      </c>
+      <c r="G94" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_42" LOC = P137 | IOSTANDARD = LVCMOS33;   # IO_L4N_0  ### PL3 Pin 34</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B95" s="11">
         <v>43</v>
@@ -4719,16 +4986,19 @@
         <v>17</v>
       </c>
       <c r="E95" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="F95" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_43" LOC = P134 | IOSTANDARD = LVCMOS33;   # IO_L34P_GCLK19_0 </v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+      <c r="F95" s="37">
+        <v>35</v>
+      </c>
+      <c r="G95" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_43" LOC = P134 | IOSTANDARD = LVCMOS33;   # IO_L34P_GCLK19_0  ### PL3 Pin 35</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B96" s="11">
         <v>44</v>
@@ -4740,16 +5010,19 @@
         <v>19</v>
       </c>
       <c r="E96" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="F96" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_44" LOC = P133 | IOSTANDARD = LVCMOS33;   # IO_L34N_GCLK18_0 </v>
-      </c>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+      <c r="F96" s="37">
+        <v>36</v>
+      </c>
+      <c r="G96" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_44" LOC = P133 | IOSTANDARD = LVCMOS33;   # IO_L34N_GCLK18_0  ### PL3 Pin 36</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B97" s="11">
         <v>45</v>
@@ -4761,16 +5034,19 @@
         <v>21</v>
       </c>
       <c r="E97" s="32" t="s">
-        <v>265</v>
-      </c>
-      <c r="F97" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_45" LOC = P132 | IOSTANDARD = LVCMOS33;   # IO_L35P_GCLK17_0 </v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+      <c r="F97" s="37">
+        <v>37</v>
+      </c>
+      <c r="G97" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_45" LOC = P132 | IOSTANDARD = LVCMOS33;   # IO_L35P_GCLK17_0  ### PL3 Pin 37</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B98" s="11">
         <v>46</v>
@@ -4782,16 +5058,19 @@
         <v>23</v>
       </c>
       <c r="E98" s="32" t="s">
-        <v>266</v>
-      </c>
-      <c r="F98" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_46" LOC = P131 | IOSTANDARD = LVCMOS33;   # IO_L35N_GCLK16_0 </v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+        <v>265</v>
+      </c>
+      <c r="F98" s="37">
+        <v>38</v>
+      </c>
+      <c r="G98" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_46" LOC = P131 | IOSTANDARD = LVCMOS33;   # IO_L35N_GCLK16_0  ### PL3 Pin 38</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B99" s="11">
         <v>47</v>
@@ -4803,16 +5082,19 @@
         <v>25</v>
       </c>
       <c r="E99" s="32" t="s">
-        <v>267</v>
-      </c>
-      <c r="F99" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_47" LOC = P127 | IOSTANDARD = LVCMOS33;   # IO_L36P_GCLK15_0 </v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+        <v>266</v>
+      </c>
+      <c r="F99" s="37">
+        <v>39</v>
+      </c>
+      <c r="G99" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_47" LOC = P127 | IOSTANDARD = LVCMOS33;   # IO_L36P_GCLK15_0  ### PL3 Pin 39</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B100" s="11">
         <v>48</v>
@@ -4824,16 +5106,19 @@
         <v>27</v>
       </c>
       <c r="E100" s="32" t="s">
-        <v>268</v>
-      </c>
-      <c r="F100" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">NET "SV2_48" LOC = P126 | IOSTANDARD = LVCMOS33;   # IO_L36N_GCLK14_0 </v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+        <v>267</v>
+      </c>
+      <c r="F100" s="37">
+        <v>40</v>
+      </c>
+      <c r="G100" t="str">
+        <f t="shared" si="2"/>
+        <v>NET "SV2_48" LOC = P126 | IOSTANDARD = LVCMOS33;   # IO_L36N_GCLK14_0  ### PL3 Pin 40</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B101" s="11">
         <v>49</v>
@@ -4845,16 +5130,16 @@
         <v>29</v>
       </c>
       <c r="E101" s="32" t="s">
-        <v>269</v>
-      </c>
-      <c r="F101" t="str">
+        <v>268</v>
+      </c>
+      <c r="G101" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">NET "SV2_49" LOC = P124 | IOSTANDARD = LVCMOS33;   # IO_L37P_GCLK13_0 </v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B102" s="11">
         <v>50</v>
@@ -4866,20 +5151,20 @@
         <v>31</v>
       </c>
       <c r="E102" s="32" t="s">
-        <v>270</v>
-      </c>
-      <c r="F102" t="str">
+        <v>269</v>
+      </c>
+      <c r="G102" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">NET "SV2_50" LOC = P123 | IOSTANDARD = LVCMOS33;   # IO_L37N_GCLK12_0 </v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D110" s="6"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D111" s="6"/>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D112" s="6"/>
     </row>
     <row r="113" spans="4:4" x14ac:dyDescent="0.25">
@@ -4892,6 +5177,1153 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G52"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="91.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C3" s="11">
+        <v>1</v>
+      </c>
+      <c r="D3" s="13"/>
+      <c r="E3" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="9" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="C4" s="11">
+        <v>2</v>
+      </c>
+      <c r="D4" s="13"/>
+      <c r="E4" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="9" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C5" s="11">
+        <v>3</v>
+      </c>
+      <c r="D5" s="13"/>
+      <c r="E5" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="F5" s="1"/>
+      <c r="G5" s="9"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="C6" s="11">
+        <v>4</v>
+      </c>
+      <c r="D6" s="13"/>
+      <c r="E6" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="F6" s="1"/>
+      <c r="G6" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="C7" s="11">
+        <v>5</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="F7" s="1"/>
+      <c r="G7" t="str">
+        <f xml:space="preserve"> CONCATENATE("NET """,$B7,""" LOC = ",$D7," | IOSTANDARD = LVCMOS33;   # ",E7," ### SV2 Pin ",C7," ###")</f>
+        <v>NET "HSYNC" LOC = P51 | IOSTANDARD = LVCMOS33;   # IO_L31P_GCLK31_D14_2 ### SV2 Pin 5 ###</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="C8" s="11">
+        <v>6</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="F8" s="1"/>
+      <c r="G8" t="str">
+        <f t="shared" ref="G8:G52" si="0" xml:space="preserve"> CONCATENATE("NET """,$B8,""" LOC = ",$D8," | IOSTANDARD = LVCMOS33;   # ",E8," ### SV2 Pin ",C8," ###")</f>
+        <v>NET "VSYNC" LOC = P50 | IOSTANDARD = LVCMOS33;   # IO_L31N_GCLK30_D15_2 ### SV2 Pin 6 ###</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>292</v>
+      </c>
+      <c r="C9" s="11">
+        <v>7</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" t="s">
+        <v>245</v>
+      </c>
+      <c r="F9" s="1"/>
+      <c r="G9" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "BLUE(2)" LOC = P41 | IOSTANDARD = LVCMOS33;   # IO_L64P_2 ### SV2 Pin 7 ###</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="C10" s="11">
+        <v>8</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="E10" t="s">
+        <v>246</v>
+      </c>
+      <c r="F10" s="1"/>
+      <c r="G10" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "BLUE(1)" LOC = P40 | IOSTANDARD = LVCMOS33;   # IO_L64N_2 ### SV2 Pin 8 ###</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C11" s="11">
+        <v>9</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="E11" t="s">
+        <v>128</v>
+      </c>
+      <c r="F11" s="1"/>
+      <c r="G11" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "BLUE(0)" LOC = P35 | IOSTANDARD = LVCMOS33;   # IO_L1P_3  ### SV2 Pin 9 ###</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>319</v>
+      </c>
+      <c r="C12" s="11">
+        <v>10</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E12" t="s">
+        <v>130</v>
+      </c>
+      <c r="F12" s="1"/>
+      <c r="G12" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "GREEN(2)" LOC = P34 | IOSTANDARD = LVCMOS33;   # IO_L1N_VREF_3  ### SV2 Pin 10 ###</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>320</v>
+      </c>
+      <c r="C13" s="11">
+        <v>11</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="E13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "GREEN(1)" LOC = P33 | IOSTANDARD = LVCMOS33;   # IO_L2P_3  ### SV2 Pin 11 ###</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="C14" s="11">
+        <v>12</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="E14" t="s">
+        <v>134</v>
+      </c>
+      <c r="F14" s="1"/>
+      <c r="G14" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "GREEN(0)" LOC = P32 | IOSTANDARD = LVCMOS33;   # IO_L2N_3  ### SV2 Pin 12 ###</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>322</v>
+      </c>
+      <c r="C15" s="11">
+        <v>13</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="E15" t="s">
+        <v>136</v>
+      </c>
+      <c r="F15" s="1"/>
+      <c r="G15" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "RED(2)" LOC = P30 | IOSTANDARD = LVCMOS33;   # IO_L36P_3  ### SV2 Pin 13 ###</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="C16" s="11">
+        <v>14</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="E16" t="s">
+        <v>138</v>
+      </c>
+      <c r="F16" s="1"/>
+      <c r="G16" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "RED(1)" LOC = P29 | IOSTANDARD = LVCMOS33;   # IO_L36N_3  ### SV2 Pin 14 ###</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="C17" s="11">
+        <v>15</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="E17" t="s">
+        <v>140</v>
+      </c>
+      <c r="F17" s="1"/>
+      <c r="G17" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "RED(0)" LOC = P27 | IOSTANDARD = LVCMOS33;   # IO_L37P_3  ### SV2 Pin 15 ###</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>295</v>
+      </c>
+      <c r="C18" s="11">
+        <v>16</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="E18" t="s">
+        <v>142</v>
+      </c>
+      <c r="F18" s="1"/>
+      <c r="G18" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "VIDEO(0)" LOC = P26 | IOSTANDARD = LVCMOS33;   # IO_L37N_3  ### SV2 Pin 16 ###</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>296</v>
+      </c>
+      <c r="C19" s="11">
+        <v>17</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F19" s="1"/>
+      <c r="G19" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "VIDEO(1)" LOC = P24 | IOSTANDARD = LVCMOS33;   # IO_L41P_GCLK27_3  ### SV2 Pin 17 ###</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>297</v>
+      </c>
+      <c r="C20" s="11">
+        <v>18</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F20" s="1"/>
+      <c r="G20" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "VIDEO(2)" LOC = P23 | IOSTANDARD = LVCMOS33;   # IO_L41N_GCLK26_3  ### SV2 Pin 18 ###</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="C21" s="11">
+        <v>19</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="F21" s="1"/>
+      <c r="G21" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "VIDEO(3)" LOC = P22 | IOSTANDARD = LVCMOS33;   # IO_L42P_GCLK25_TRDY2_3  ### SV2 Pin 19 ###</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="C22" s="11">
+        <v>20</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="F22" s="1"/>
+      <c r="G22" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "VIDEO(4)" LOC = P21 | IOSTANDARD = LVCMOS33;   # IO_L42N_GCLK24_3  ### SV2 Pin 20 ###</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>300</v>
+      </c>
+      <c r="C23" s="11">
+        <v>21</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "VIDEO(5)" LOC = P17 | IOSTANDARD = LVCMOS33;   # IO_L43P_GCLK23_3  ### SV2 Pin 21 ###</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="C24" s="11">
+        <v>22</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>153</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="F24" s="1"/>
+      <c r="G24" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "VIDEO(6)" LOC = P16 | IOSTANDARD = LVCMOS33;   # IO_L43N_GCLK22_IRDY2_3  ### SV2 Pin 22 ###</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>302</v>
+      </c>
+      <c r="C25" s="11">
+        <v>23</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="F25" s="1"/>
+      <c r="G25" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "VIDEO(7)" LOC = P15 | IOSTANDARD = LVCMOS33;   # IO_L44P_GCLK21_3  ### SV2 Pin 23 ###</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>318</v>
+      </c>
+      <c r="C26" s="11">
+        <v>24</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="F26" s="1"/>
+      <c r="G26" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "CARRIER" LOC = P14 | IOSTANDARD = LVCMOS33;   # IO_L44N_GCLK20_3  ### SV2 Pin 24 ###</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B27" s="8" t="str">
+        <f t="shared" ref="B4:B52" si="1">CONCATENATE(A27,"_",C27)</f>
+        <v>SV2_25</v>
+      </c>
+      <c r="C27" s="11">
+        <v>25</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="E27" t="s">
+        <v>160</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "SV2_25" LOC = P12 | IOSTANDARD = LVCMOS33;   # IO_L49P_3  ### SV2 Pin 25 ###</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B28" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>SV2_26</v>
+      </c>
+      <c r="C28" s="11">
+        <v>26</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="E28" t="s">
+        <v>162</v>
+      </c>
+      <c r="F28" s="1"/>
+      <c r="G28" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "SV2_26" LOC = P11 | IOSTANDARD = LVCMOS33;   # IO_L49N_3  ### SV2 Pin 26 ###</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B29" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>SV2_27</v>
+      </c>
+      <c r="C29" s="11">
+        <v>27</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="E29" t="s">
+        <v>164</v>
+      </c>
+      <c r="F29" s="1"/>
+      <c r="G29" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "SV2_27" LOC = P10 | IOSTANDARD = LVCMOS33;   # IO_L50P_3  ### SV2 Pin 27 ###</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B30" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>SV2_28</v>
+      </c>
+      <c r="C30" s="11">
+        <v>28</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="E30" t="s">
+        <v>166</v>
+      </c>
+      <c r="F30" s="1"/>
+      <c r="G30" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "SV2_28" LOC = P9 | IOSTANDARD = LVCMOS33;   # IO_L50N_3  ### SV2 Pin 28 ###</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B31" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>SV2_29</v>
+      </c>
+      <c r="C31" s="11">
+        <v>29</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>167</v>
+      </c>
+      <c r="E31" t="s">
+        <v>168</v>
+      </c>
+      <c r="F31" s="1"/>
+      <c r="G31" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "SV2_29" LOC = P8 | IOSTANDARD = LVCMOS33;   # IO_L51P_3  ### SV2 Pin 29 ###</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B32" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>SV2_30</v>
+      </c>
+      <c r="C32" s="11">
+        <v>30</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="E32" t="s">
+        <v>170</v>
+      </c>
+      <c r="F32" s="1"/>
+      <c r="G32" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "SV2_30" LOC = P7 | IOSTANDARD = LVCMOS33;   # IO_L51N_3  ### SV2 Pin 30 ###</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B33" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>SV2_31</v>
+      </c>
+      <c r="C33" s="11">
+        <v>31</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="E33" t="s">
+        <v>172</v>
+      </c>
+      <c r="F33" s="1"/>
+      <c r="G33" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "SV2_31" LOC = P6 | IOSTANDARD = LVCMOS33;   # IO_L52P_3  ### SV2 Pin 31 ###</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="C34" s="11">
+        <v>32</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="E34" t="s">
+        <v>174</v>
+      </c>
+      <c r="F34" s="1"/>
+      <c r="G34" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "COIN" LOC = P5 | IOSTANDARD = LVCMOS33;   # IO_L52N_3  ### SV2 Pin 32 ###</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="C35" s="11">
+        <v>33</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="E35" t="s">
+        <v>176</v>
+      </c>
+      <c r="F35" s="1"/>
+      <c r="G35" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "START_1" LOC = P2 | IOSTANDARD = LVCMOS33;   # IO_L83P_3  ### SV2 Pin 33 ###</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="C36" s="11">
+        <v>34</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="E36" t="s">
+        <v>178</v>
+      </c>
+      <c r="F36" s="1"/>
+      <c r="G36" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "LEFT" LOC = P1 | IOSTANDARD = LVCMOS33;   # IO_L83N_VREF_3  ### SV2 Pin 34 ###</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="C37" s="11">
+        <v>35</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>0</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1</v>
+      </c>
+      <c r="F37" s="1"/>
+      <c r="G37" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "RIGHT" LOC = P144 | IOSTANDARD = LVCMOS33;   # IO_L1P_HSWAPEN_0  ### SV2 Pin 35 ###</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="C38" s="11">
+        <v>36</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>2</v>
+      </c>
+      <c r="E38" t="s">
+        <v>3</v>
+      </c>
+      <c r="F38" s="1"/>
+      <c r="G38" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "FIRE" LOC = P143 | IOSTANDARD = LVCMOS33;   # IO_L1N_VREF_0  ### SV2 Pin 36 ###</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>308</v>
+      </c>
+      <c r="C39" s="11">
+        <v>37</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E39" t="s">
+        <v>5</v>
+      </c>
+      <c r="F39" s="1"/>
+      <c r="G39" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "START_2" LOC = P142 | IOSTANDARD = LVCMOS33;   # IO_L2P_0  ### SV2 Pin 37 ###</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="C40" s="11">
+        <v>38</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40" t="s">
+        <v>7</v>
+      </c>
+      <c r="F40" s="1"/>
+      <c r="G40" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "UP" LOC = P141 | IOSTANDARD = LVCMOS33;   # IO_L2N_0  ### SV2 Pin 38 ###</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="C41" s="11">
+        <v>39</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="1"/>
+      <c r="G41" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "DOWN" LOC = P140 | IOSTANDARD = LVCMOS33;   # IO_L3P_0  ### SV2 Pin 39 ###</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B42" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>SV2_40</v>
+      </c>
+      <c r="C42" s="11">
+        <v>40</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" t="s">
+        <v>11</v>
+      </c>
+      <c r="F42" s="1"/>
+      <c r="G42" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "SV2_40" LOC = P139 | IOSTANDARD = LVCMOS33;   # IO_L3N_0  ### SV2 Pin 40 ###</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="C43" s="11">
+        <v>41</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="1"/>
+      <c r="G43" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "AUDIO_PWM" LOC = P138 | IOSTANDARD = LVCMOS33;   # IO_L4P_0  ### SV2 Pin 41 ###</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B44" s="8" t="str">
+        <f t="shared" si="1"/>
+        <v>SV2_42</v>
+      </c>
+      <c r="C44" s="11">
+        <v>42</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E44" t="s">
+        <v>15</v>
+      </c>
+      <c r="F44" s="1"/>
+      <c r="G44" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "SV2_42" LOC = P137 | IOSTANDARD = LVCMOS33;   # IO_L4N_0  ### SV2 Pin 42 ###</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>326</v>
+      </c>
+      <c r="C45" s="11">
+        <v>43</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F45" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="G45" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "LED(0)" LOC = P134 | IOSTANDARD = LVCMOS33;   # IO_L34P_GCLK19_0  ### SV2 Pin 43 ###</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>311</v>
+      </c>
+      <c r="C46" s="11">
+        <v>44</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="F46" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="G46" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "LED(1)" LOC = P133 | IOSTANDARD = LVCMOS33;   # IO_L34N_GCLK18_0  ### SV2 Pin 44 ###</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="C47" s="11">
+        <v>45</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F47" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="G47" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "LED(2)" LOC = P132 | IOSTANDARD = LVCMOS33;   # IO_L35P_GCLK17_0  ### SV2 Pin 45 ###</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="C48" s="11">
+        <v>46</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F48" s="32" t="s">
+        <v>265</v>
+      </c>
+      <c r="G48" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "LED(3)" LOC = P131 | IOSTANDARD = LVCMOS33;   # IO_L35N_GCLK16_0  ### SV2 Pin 46 ###</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="C49" s="11">
+        <v>47</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="G49" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "LED(4)" LOC = P127 | IOSTANDARD = LVCMOS33;   # IO_L36P_GCLK15_0  ### SV2 Pin 47 ###</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B50" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="C50" s="11">
+        <v>48</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F50" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="G50" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "LED(5)" LOC = P126 | IOSTANDARD = LVCMOS33;   # IO_L36N_GCLK14_0  ### SV2 Pin 48 ###</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="C51" s="11">
+        <v>49</v>
+      </c>
+      <c r="D51" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F51" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="G51" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "LED(6)" LOC = P124 | IOSTANDARD = LVCMOS33;   # IO_L37P_GCLK13_0  ### SV2 Pin 49 ###</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B52" s="8" t="s">
+        <v>317</v>
+      </c>
+      <c r="C52" s="11">
+        <v>50</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F52" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="G52" t="str">
+        <f t="shared" si="0"/>
+        <v>NET "LED(7)" LOC = P123 | IOSTANDARD = LVCMOS33;   # IO_L37N_GCLK12_0  ### SV2 Pin 50 ###</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4914,29 +6346,29 @@
   <sheetData>
     <row r="1" spans="1:15" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>218</v>
-      </c>
       <c r="C1" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E1" s="18" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="F1" s="18"/>
       <c r="G1" s="27" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1" s="26" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="J1" s="27"/>
       <c r="K1" s="26"/>
@@ -4945,7 +6377,7 @@
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B2" s="11">
         <v>15</v>
@@ -4960,7 +6392,7 @@
         <v>3</v>
       </c>
       <c r="G2" s="27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H2" s="4">
         <v>7</v>
@@ -4978,7 +6410,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B3" s="11">
         <v>17</v>
@@ -4993,7 +6425,7 @@
         <v>4</v>
       </c>
       <c r="G3" s="27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H3" s="4">
         <v>6</v>
@@ -5011,7 +6443,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B4" s="11">
         <v>19</v>
@@ -5026,7 +6458,7 @@
         <v>5</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H4" s="4">
         <v>5</v>
@@ -5044,7 +6476,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B5" s="11">
         <v>21</v>
@@ -5059,7 +6491,7 @@
         <v>6</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H5" s="4">
         <v>4</v>
@@ -5077,7 +6509,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B6" s="11">
         <v>23</v>
@@ -5092,7 +6524,7 @@
         <v>7</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H6" s="4">
         <v>3</v>
@@ -5110,7 +6542,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B7" s="11">
         <v>25</v>
@@ -5125,7 +6557,7 @@
         <v>8</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H7" s="4">
         <v>2</v>
@@ -5143,7 +6575,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B8" s="11">
         <v>27</v>
@@ -5158,7 +6590,7 @@
         <v>9</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H8" s="4">
         <v>1</v>
@@ -5176,7 +6608,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B9" s="11">
         <v>29</v>
@@ -5191,7 +6623,7 @@
         <v>10</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H9" s="4">
         <v>0</v>
@@ -5209,7 +6641,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B10" s="11">
         <v>31</v>
@@ -5224,7 +6656,7 @@
         <v>11</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H10" s="4">
         <v>0</v>
@@ -5242,7 +6674,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B11" s="11">
         <v>33</v>
@@ -5257,7 +6689,7 @@
         <v>12</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H11" s="4">
         <v>1</v>
@@ -5275,7 +6707,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B12" s="11">
         <v>35</v>
@@ -5290,7 +6722,7 @@
         <v>13</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H12" s="4">
         <v>2</v>
@@ -5308,7 +6740,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B13" s="11">
         <v>38</v>
@@ -5323,7 +6755,7 @@
         <v>15</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H13" s="4">
         <v>3</v>
@@ -5341,7 +6773,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B14" s="11">
         <v>36</v>
@@ -5356,7 +6788,7 @@
         <v>16</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H14" s="4">
         <v>4</v>
@@ -5374,7 +6806,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B15" s="11">
         <v>34</v>
@@ -5389,7 +6821,7 @@
         <v>17</v>
       </c>
       <c r="G15" s="27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H15" s="4">
         <v>5</v>
@@ -5407,7 +6839,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B16" s="11">
         <v>32</v>
@@ -5422,7 +6854,7 @@
         <v>18</v>
       </c>
       <c r="G16" s="27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H16" s="4">
         <v>6</v>
@@ -5440,7 +6872,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B17" s="11">
         <v>30</v>
@@ -5455,7 +6887,7 @@
         <v>19</v>
       </c>
       <c r="G17" s="27" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H17" s="4">
         <v>7</v>
@@ -5473,7 +6905,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B18" s="11">
         <v>26</v>
@@ -5488,7 +6920,7 @@
         <v>21</v>
       </c>
       <c r="G18" s="27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H18" s="4">
         <v>10</v>
@@ -5506,7 +6938,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B19" s="11">
         <v>20</v>
@@ -5521,7 +6953,7 @@
         <v>24</v>
       </c>
       <c r="G19" s="27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H19" s="4">
         <v>9</v>
@@ -5539,7 +6971,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B20" s="11">
         <v>18</v>
@@ -5554,7 +6986,7 @@
         <v>25</v>
       </c>
       <c r="G20" s="27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H20" s="4">
         <v>8</v>
@@ -5575,7 +7007,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B22" s="11">
         <v>11</v>
@@ -5592,7 +7024,7 @@
       <c r="F22" s="14"/>
       <c r="G22" s="31"/>
       <c r="H22" s="30" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="I22" s="14" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,H22,""" LOC = ",$C22," | IOSTANDARD = LVCMOS33;  # ",$D22,", ",$A22," Pin ",$B22)</f>
@@ -5607,7 +7039,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B23" s="11">
         <v>13</v>
@@ -5623,7 +7055,7 @@
       </c>
       <c r="G23" s="27"/>
       <c r="H23" s="30" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I23" s="14" t="str">
         <f t="shared" ref="I23:I24" si="1" xml:space="preserve"> CONCATENATE("NET """,H23,""" LOC = ",$C23," | IOSTANDARD = LVCMOS33;  # ",$D23,", ",$A23," Pin ",$B23)</f>
@@ -5638,7 +7070,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B24" s="11">
         <v>16</v>
@@ -5654,7 +7086,7 @@
       </c>
       <c r="G24" s="27"/>
       <c r="H24" s="30" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I24" s="14" t="str">
         <f t="shared" si="1"/>
@@ -5669,7 +7101,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B25" s="11">
         <v>14</v>
@@ -5686,7 +7118,7 @@
       <c r="F25" s="20"/>
       <c r="G25" s="31"/>
       <c r="H25" s="30" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I25" s="14" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,H25,""" LOC = ",$C25," | IOSTANDARD = LVCMOS33 | PULLUP;  # ",$D25,", ",$A25," Pin ",$B25)</f>
@@ -5713,7 +7145,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B27" s="11">
         <v>28</v>
@@ -5730,7 +7162,7 @@
       <c r="F27" s="14"/>
       <c r="G27" s="29"/>
       <c r="H27" s="30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="I27" s="14" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,H27,""" LOC = ",$C27," | IOSTANDARD = LVCMOS33 | PULLUP;  # ",$D27,", ",$A27," Pin ",$B27)</f>
@@ -5745,7 +7177,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B28" s="11">
         <v>24</v>
@@ -5762,7 +7194,7 @@
       <c r="F28" s="14"/>
       <c r="G28" s="29"/>
       <c r="H28" s="30" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I28" s="14" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,H28,""" LOC = ",$C28," | IOSTANDARD = LVCMOS33 | PULLUP;  # ",$D28,", ",$A28," Pin ",$B28)</f>
@@ -5777,7 +7209,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B29" s="11">
         <v>22</v>
@@ -5793,7 +7225,7 @@
       </c>
       <c r="G29" s="27"/>
       <c r="H29" s="30" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="I29" s="14" t="str">
         <f xml:space="preserve"> CONCATENATE("NET """,H29,""" LOC = ",$C29," | IOSTANDARD = LVCMOS33 | PULLUP;  # ",$D29,", ",$A29," Pin ",$B29)</f>
